--- a/tools/precos/planilhas/precos-oficiais-COSRX.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-COSRX.xlsx
@@ -570,12 +570,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MB000752</t>
+          <t>MB000819</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Peptide-132 Ultra Perfect Hair Bonding Shampoo: shampoo reconstrutor para cabelo · Single / 100mL</t>
+          <t>5 Peptide B5 Sensitive Repair Salve Lip Balm: bálsamo labial reparador 12 g</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>108.9</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -593,20 +593,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>COSRX PEPTIDE-132 Ultra Perfect Hair Bonding Shampoo</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>100mL / Single</t>
-        </is>
-      </c>
+          <t>5 Peptide B5 Sensitive Repair Salve Lip Balm</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" s="4" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>12</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I2" s="4" t="n"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -614,7 +608,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-shampoo-번들?variant=52270322680024</t>
+          <t>https://cosrx.com/products/5-peptide-b5-sensitive-repair-salve-lip-balm</t>
         </is>
       </c>
       <c r="L2" s="2">
@@ -629,12 +623,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MB000819</t>
+          <t>MB003440</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5 Peptide B5 Sensitive Repair Salve Lip Balm: bálsamo labial reparador 12 g</t>
+          <t>AC Collection Acne Patch: adesivos ovais para espinhas com centella (26 unidades)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -643,21 +637,21 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>57.9</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5 Peptide B5 Sensitive Repair Salve Lip Balm</t>
+          <t>AC Collection Acne Patch</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="4" t="n">
-        <v>15</v>
+        <v>8.99</v>
       </c>
       <c r="I3" s="4" t="n"/>
       <c r="J3" t="inlineStr">
@@ -667,7 +661,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/5-peptide-b5-sensitive-repair-salve-lip-balm</t>
+          <t>https://cosrx.com/products/ac-collection-acne-patch</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -682,12 +676,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MB003440</t>
+          <t>MB003463</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AC Collection Acne Patch: adesivos ovais para espinhas com centella (26 unidades)</t>
+          <t>Acne Pimple Master Patch: adesivos para espinhas (24 unidades)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -696,21 +690,21 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>42.9</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AC Collection Acne Patch</t>
+          <t>Acne Pimple Master Patch</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" s="4" t="n">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
       <c r="I4" s="4" t="n"/>
       <c r="J4" t="inlineStr">
@@ -720,7 +714,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/ac-collection-acne-patch</t>
+          <t>https://cosrx.com/products/acne-pimple-master-patch</t>
         </is>
       </c>
       <c r="L4" s="2">
@@ -735,12 +729,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB003452</t>
+          <t>MB003454</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AC Collection Calming Liquid Intensive: essência calmante com própolis e BHA 125 ml</t>
+          <t>Advanced Snail Hydrogel Eye Patch: adesivos de hidrogel para os olhos (60 unidades)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -749,25 +743,25 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>188.9</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>203.9</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AC Collection Calming Liquid Intensive</t>
+          <t>Advanced Snail Hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.22 fl.oz / 125ml</t>
+          <t>60 patches / 3.17 oz</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I5" s="4" t="n"/>
       <c r="J5" t="inlineStr">
@@ -777,7 +771,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/ac-collection-calming-liquid-intensive</t>
+          <t>https://cosrx.com/products/advanced-snail-hydrogel-eye-patch-copy</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -792,12 +786,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB003377</t>
+          <t>MB000789</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AC Collection: sérum para a aparência de manchas e marquinhas de espinhas</t>
+          <t>Advanced Snail Mucin Glass Glow Hydrogel Mask: máscara de hidrogel com mucina de caracol · 3ea</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,21 +800,25 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>196.9</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>108.9</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AC Collection Acne Patch</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Advanced Snail Mucin Glass Glow Hydrogel Mask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3ea</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="n">
-        <v>8.99</v>
+        <v>15</v>
       </c>
       <c r="I6" s="4" t="n"/>
       <c r="J6" t="inlineStr">
@@ -830,7 +828,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/ac-collection-acne-patch</t>
+          <t>https://cosrx.com/products/advanced-snail-mucin-glass-glow-hydrogel-mask_new?variant=52394338189528</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -845,12 +843,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB003463</t>
+          <t>MB003455</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Acne Pimple Master Patch: adesivos para espinhas (24 unidades)</t>
+          <t>Advanced Snail Mucin Power Sheet Mask: máscara de mucina de caracol (10 unidades)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -859,23 +857,25 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>126.9</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Acne Pimple Master Patch</t>
+          <t>Advanced Snail Mucin Power Sheet Mask 10 Sheets</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="I7" s="4" t="n"/>
+        <v>17.5</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -883,7 +883,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/acne-pimple-master-patch</t>
+          <t>https://cosrx.com/products/cosrx-advanced-snail-mucin-power-sheet-mask-10-sheets</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -898,12 +898,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB003454</t>
+          <t>MB003414</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Advanced Snail Hydrogel Eye Patch: adesivos de hidrogel para os olhos (60 unidades)</t>
+          <t>Airy-Light Oil Control Clear Sunscreen Stick: protetor solar em bastão FPS 50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -912,25 +912,21 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>203.9</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>116.9</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Advanced Snail Hydrogel Eye Patch</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>60 patches / 3.17 oz</t>
-        </is>
-      </c>
+          <t>COSRX AIRY-LIGHT OIL CONTROL CLEAR SUNSCREEN STICK SPF 50</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I8" s="4" t="n"/>
       <c r="J8" t="inlineStr">
@@ -940,7 +936,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/advanced-snail-hydrogel-eye-patch-copy</t>
+          <t>https://cosrx.com/products/cosrx-airy-light-clear-sunscreen-stick</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -955,12 +951,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB000789</t>
+          <t>MB003432</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Advanced Snail Mucin Glass Glow Hydrogel Mask: máscara de hidrogel com mucina de caracol · 3ea</t>
+          <t>Balancium Comfort Ceramide Cream: creme com ceramida para pele sensível 80 g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -969,25 +965,21 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>188.9</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Advanced Snail Mucin Glass Glow Hydrogel Mask</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3ea</t>
-        </is>
-      </c>
+          <t>Balancium Comfort Ceramide Cream</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I9" s="4" t="n"/>
       <c r="J9" t="inlineStr">
@@ -997,7 +989,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/advanced-snail-mucin-glass-glow-hydrogel-mask_new?variant=52394338189528</t>
+          <t>https://cosrx.com/products/balancium-comfort-ceramide-cream-copy</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -1012,12 +1004,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB003455</t>
+          <t>MB003462</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Advanced Snail Mucin Power Sheet Mask: máscara de mucina de caracol (10 unidades)</t>
+          <t>Balancium Comfort Ceramide Soft Cream Sheet Mask: máscara cremosa de ceramida</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1026,25 +1018,27 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>42.9</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Advanced Snail Mucin Power Sheet Mask 10 Sheets</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Balancium Comfort Ceramide Soft Cream Sheet Mask</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1 ea</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>25</v>
-      </c>
+        <v>6.99</v>
+      </c>
+      <c r="I10" s="4" t="n"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1052,7 +1046,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-advanced-snail-mucin-power-sheet-mask-10-sheets</t>
+          <t>https://cosrx.com/products/comfort-ceramide-soft-cream-sheet-mask</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -1067,12 +1061,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB003434</t>
+          <t>MB003480</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Advanced Snail Peptide Eye Cream: creme para os olhos com caracol e peptídeos 25 ml</t>
+          <t>COSRX The Niacinamide 15 Serum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1081,25 +1075,25 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>203.9</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>144.9</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Advanced Snail Peptide Eye Cream</t>
+          <t>The Niacinamide 15 Serum</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.85 fl.oz / 25ml</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I11" s="4" t="n"/>
       <c r="J11" t="inlineStr">
@@ -1109,7 +1103,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/advanced-snail-peptide-eye-cream</t>
+          <t>https://cosrx.com/products/the-niacinamide-15-serum-번들?variant=52274229510360</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1124,12 +1118,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB003425</t>
+          <t>MB003416</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Advanced Snail Radiance Dual Essence: essência dupla de caracol e niacinamida 80 ml</t>
+          <t>Centella Blemish Cream: creme de centella para marquinhas 30 g</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1138,25 +1132,21 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>141.9</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>152.9</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Advanced Snail Radiance Dual Essence</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2.70 fl.oz / 80ml</t>
-        </is>
-      </c>
+          <t>Centella Blemish Cream</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I12" s="4" t="n"/>
       <c r="J12" t="inlineStr">
@@ -1166,7 +1156,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/advanced-snail-radiance-dual-essence</t>
+          <t>https://cosrx.com/products/centella-blemish-cream</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1181,12 +1171,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB003414</t>
+          <t>MB003403</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Airy-Light Oil Control Clear Sunscreen Stick: protetor solar em bastão FPS 50</t>
+          <t>Double Peptide Firming Duo: sérum 6 Peptide + sérum Blue Peptide Bakuchiol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1195,23 +1185,25 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>321.9</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COSRX AIRY-LIGHT OIL CONTROL CLEAR SUNSCREEN STICK SPF 50</t>
+          <t>Double Peptide Firming Duo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I13" s="4" t="n"/>
+        <v>44.2</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>52</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1219,7 +1211,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-airy-light-clear-sunscreen-stick</t>
+          <t>https://cosrx.com/products/peptide-firming-duo</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1234,12 +1226,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB003432</t>
+          <t>MB003444</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Balancium Comfort Ceramide Cream: creme com ceramida para pele sensível 80 g</t>
+          <t>Full Fit Honey Sugar Lip Scrub: esfoliante labial de açúcar e mel 20 g</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1248,21 +1240,21 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>188.9</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Balancium Comfort Ceramide Cream</t>
+          <t>Lip Scrub - Full Fit Honey Sugar Lip Scrub</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" t="inlineStr">
@@ -1272,7 +1264,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/balancium-comfort-ceramide-cream-copy</t>
+          <t>https://cosrx.com/products/lip-scrub-full-fit-propolis-honey-sugar-lip-scrub</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1287,12 +1279,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB003462</t>
+          <t>MB000733</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Balancium Comfort Ceramide Soft Cream Sheet Mask: máscara cremosa de ceramida</t>
+          <t>Full Fit Propolis Honey Overnight Mask: máscara noturna de própolis e mel 60 ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1301,25 +1293,21 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>130.9</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Balancium Comfort Ceramide Soft Cream Sheet Mask</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1 ea</t>
-        </is>
-      </c>
+          <t>Full Fit Propolis Honey Overnight Mask</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" s="4" t="n">
-        <v>6.99</v>
+        <v>18</v>
       </c>
       <c r="I15" s="4" t="n"/>
       <c r="J15" t="inlineStr">
@@ -1329,7 +1317,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/comfort-ceramide-soft-cream-sheet-mask</t>
+          <t>https://cosrx.com/products/full-fit-propolis-honey-overnight-mask_cpnp</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1344,12 +1332,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB000777</t>
+          <t>MB003422</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COSRX Aloe Soothing Sun Cream FPS 50+ PA+++: protetor solar calmante de aloe 50 ml</t>
+          <t>Full Fit Propolis Nourishing Magnet Sheet Mask: máscara de própolis e mel (1 unidade)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,31 +1346,31 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>115.9</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>42.9</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aloe Soothing Sun Cream  SPF50+/ PA+++</t>
+          <t>Full Fit Propolis Nourishing Magnet Sheet Mask</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" s="4" t="n">
-        <v>16</v>
+        <v>6.99</v>
       </c>
       <c r="I16" s="4" t="n"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/aloe-soothing-sun-cream-spf50-pa</t>
+          <t>https://cosrx.com/products/propolis-nourishing-magnet-sheet-mask</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1397,12 +1385,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB003471</t>
+          <t>MB003446</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COSRX Red Rice &amp; Inositol Deep Pore Cleansing Exfoliator</t>
+          <t>Hyaluronic Acid Hydra Power Essence: essência de ácido hialurônico 100 ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1411,21 +1399,21 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>181.9</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>COSRX RED RICE INOSITOL Pore Clarifying Deep Cleanser</t>
+          <t>Hyaluronic Acid Hydra Power Essence</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I17" s="4" t="n"/>
       <c r="J17" t="inlineStr">
@@ -1435,7 +1423,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-red-rice-inositol-pore-clarifying-deep-cleanser</t>
+          <t>https://cosrx.com/products/hyaluronic-acid-hydra-power-essence</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1450,12 +1438,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB003480</t>
+          <t>MB003459</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COSRX The Niacinamide 15 Serum</t>
+          <t>Hyaluronic Acid Intensive Cream: creme de ácido hialurônico 100 g</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1464,29 +1452,23 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>181.9</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The Niacinamide 15 Serum</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2-Pack</t>
-        </is>
-      </c>
+          <t>Hyaluronic Acid Intensive Cream</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I18" s="4" t="n"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1494,7 +1476,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-niacinamide-15-serum-번들?variant=52274229543128</t>
+          <t>https://cosrx.com/products/hyaluronic-acid-intensive-cream</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1509,12 +1491,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB003416</t>
+          <t>MB003413</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Centella Blemish Cream: creme de centella para marquinhas 30 g</t>
+          <t>Hydrium Triple Hyaluronic Water Wave Sheet Mask: máscara hidratante (1 unidade)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1523,31 +1505,31 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>42.9</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Centella Blemish Cream</t>
+          <t>Hydrium Triple Hyaluronic Water Wave Sheet Mask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" s="4" t="n">
-        <v>21</v>
+        <v>6.99</v>
       </c>
       <c r="I19" s="4" t="n"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/centella-blemish-cream</t>
+          <t>https://cosrx.com/products/triple-hyaluronic-water-wave-sheet-mask</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1562,12 +1544,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB003376</t>
+          <t>MB003420</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Clear Fit Master Patch: adesivos ultrafinos e foscos para espinhas (18 unidades)</t>
+          <t>Lip Plump Refresh AHA BHA Vitamin C: volumizador labial 20 g</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1576,25 +1558,23 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Clear Fit Master Patch</t>
+          <t>Lip Plump - Refresh AHA BHA Vitamin C Lip Plumper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>6.99</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I20" s="4" t="n"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1602,7 +1582,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/clear-fit-master-patch</t>
+          <t>https://cosrx.com/products/lip-plump-refresh-aha-bha-viamin-c-lip-plumper</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1617,12 +1597,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003403</t>
+          <t>MB003423</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Double Peptide Firming Duo: sérum 6 Peptide + sérum Blue Peptide Bakuchiol</t>
+          <t>Lip Sleep Balancium Ceramide Lip Butter: máscara labial noturna 20 g</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1631,25 +1611,23 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>321.9</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Double Peptide Firming Duo</t>
+          <t>Lip Sleep - Balancium Ceramide Lip Butter Sleeping Mask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" s="4" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>52</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I21" s="4" t="n"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1657,7 +1635,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/peptide-firming-duo</t>
+          <t>https://cosrx.com/products/lip-sleep-balancium-ceramide-lip-butter-sleeping-mask</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1672,12 +1650,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003444</t>
+          <t>MB003390</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Full Fit Honey Sugar Lip Scrub: esfoliante labial de açúcar e mel 20 g</t>
+          <t>Low pH Micellar Water with Niacinamide</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1686,23 +1664,29 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lip Scrub - Full Fit Honey Sugar Lip Scrub</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Low pH Niacinamide Micellar Cleansing Water</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Single (400mL)</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" s="4" t="n"/>
+        <v>10.5</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1710,7 +1694,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/lip-scrub-full-fit-propolis-honey-sugar-lip-scrub</t>
+          <t>https://cosrx.com/products/low-ph-niacinamide-micellar-cleansing-water?variant=43891424231640</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1725,12 +1709,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB000733</t>
+          <t>MB000708</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Full Fit Propolis Honey Overnight Mask: máscara noturna de própolis e mel 60 ml</t>
+          <t>Low pH Niacinamide Micellar Cleansing Water: água micelar de pH baixo · 2-step Daily Deep Cleansing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1739,23 +1723,29 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>130.9</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>210.9</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Full Fit Propolis Honey Overnight Mask</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Low pH Niacinamide Micellar Cleansing Water</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Single (400mL)</t>
+        </is>
+      </c>
       <c r="H23" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I23" s="4" t="n"/>
+        <v>10.5</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1763,7 +1753,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/full-fit-propolis-honey-overnight-mask_cpnp</t>
+          <t>https://cosrx.com/products/low-ph-niacinamide-micellar-cleansing-water?variant=43891424231640</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1778,12 +1768,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB000732</t>
+          <t>MB000709</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Full Fit Propolis Light Ampoule: ampola de própolis 30 ml</t>
+          <t>Low pH Niacinamide Micellar Cleansing Water: água micelar de pH baixo · 3-step Total Cleansing Solution</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1792,27 +1782,29 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>203.9</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>327.9</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Full fit Propolis Light Ampoule</t>
+          <t>Low pH Niacinamide Micellar Cleansing Water</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.01 fl.oz/30ml</t>
+          <t>Single (400mL)</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="I24" s="4" t="n"/>
+        <v>10.5</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1820,7 +1812,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/full-fit-propolis-light-ampoule_cpnp</t>
+          <t>https://cosrx.com/products/low-ph-niacinamide-micellar-cleansing-water?variant=43891424231640</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1835,12 +1827,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB003422</t>
+          <t>MB003450</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Full Fit Propolis Nourishing Magnet Sheet Mask: máscara de própolis e mel (1 unidade)</t>
+          <t>Master Patch Basic: adesivos para espinhas 12 mm (36 unidades)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1849,21 +1841,25 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>86.90000000000001</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Full Fit Propolis Nourishing Magnet Sheet Mask</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Master Patch Basic [36ea]</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>36ea</t>
+        </is>
+      </c>
       <c r="H25" s="4" t="n">
-        <v>6.99</v>
+        <v>12</v>
       </c>
       <c r="I25" s="4" t="n"/>
       <c r="J25" t="inlineStr">
@@ -1873,7 +1869,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/propolis-nourishing-magnet-sheet-mask</t>
+          <t>https://cosrx.com/products/master-patch-basic-36-ea</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1888,12 +1884,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB003461</t>
+          <t>MB003465</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Full Fit Propolis Synergy Toner: tônico de própolis e mel</t>
+          <t>Master Patch Intensive: adesivos para espinhas em 2 tamanhos (90 unidades)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1902,25 +1898,21 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>181.9</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Full Fit Propolis Synergy Toner</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>5.07 fl.oz / 150mL</t>
-        </is>
-      </c>
+          <t>Master Patch Intensive [90ea]</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I26" s="4" t="n"/>
       <c r="J26" t="inlineStr">
@@ -1930,7 +1922,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/full-fit-propolis-synergy-toner_cpnp</t>
+          <t>https://cosrx.com/products/master-patch-intensive-90ea_cpnp</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1945,12 +1937,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB003446</t>
+          <t>MB003408</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hyaluronic Acid Hydra Power Essence: essência de ácido hialurônico 100 ml</t>
+          <t>PDRN Glass Skin Duo: sérum 5 PDRN com colágeno + máscara peel-off Exosome</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1959,23 +1951,25 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>259.9</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hyaluronic Acid Hydra Power Essence</t>
+          <t>PDRN Glass Skin Duo</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I27" s="4" t="n"/>
+        <v>35.7</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>42</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1983,7 +1977,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/hyaluronic-acid-hydra-power-essence</t>
+          <t>https://cosrx.com/products/pdrn-glass-skin-duo</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -1998,12 +1992,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB003459</t>
+          <t>MB003406</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hyaluronic Acid Intensive Cream: creme de ácido hialurônico 100 g</t>
+          <t>PDRN Premium Routine Kit: tônico + sérum + máscaras + adesivos com PDRN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2012,23 +2006,25 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>637.9</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hyaluronic Acid Intensive Cream</t>
+          <t>PDRN Premium Routine Kit</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" s="4" t="n"/>
+        <v>89.25</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>105</v>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2036,7 +2032,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/hyaluronic-acid-intensive-cream</t>
+          <t>https://cosrx.com/products/pdrn-premium-routine-kit_뉴번들</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2051,12 +2047,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB003382</t>
+          <t>MB000688</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hydrium Green Tea Aqua Soothing Gel Cream: gel-creme calmante de chá verde 50 ml</t>
+          <t>Peptide Special Care Duo: adesivos para os olhos + máscaras de hidrogel com peptídeos</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2065,27 +2061,25 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>234.9</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hydrium Green Tea Aqua Soothing Gel Cream</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1.69 fl.oz / 50ml</t>
-        </is>
-      </c>
+          <t>Peptide Special Care Duo</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I29" s="4" t="n"/>
+        <v>32.3</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>38</v>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2093,7 +2087,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/hydrium-green-tea-aqua-soothing-gel-cream</t>
+          <t>https://cosrx.com/products/peptide-special-care-duo</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2108,12 +2102,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB003456</t>
+          <t>MB000756</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hydrium Moisture Power Enriched Cream: creme hidratante intensivo 50 ml</t>
+          <t>Peptide-132 Hair Bonding Mini Kit: shampoo + tratamento + óleo-sérum para cabelo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2122,27 +2116,25 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>235.9</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hydrium Moisture Power Enriched Cream</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1.69 fl.oz / 50ml</t>
-        </is>
-      </c>
+          <t>COSRX PEPTIDE-132 Hair Bonding Mini Kit</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I30" s="4" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>36</v>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2150,7 +2142,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/hydrium-moisture-power-enriched-cream</t>
+          <t>https://cosrx.com/products/cosrx-peptide-132-hair-bonding-mini-kit</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2165,12 +2157,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB003413</t>
+          <t>MB000686</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hydrium Triple Hyaluronic Water Wave Sheet Mask: máscara hidratante (1 unidade)</t>
+          <t>Peptide-132 Hair Home Care Duo: shampoo 400 ml + máscara reconstrutora 240 ml</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2179,31 +2171,33 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>370.9</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hydrium Triple Hyaluronic Water Wave Sheet Mask</t>
+          <t>Peptide-132 Hair Home Care Duo</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" s="4" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="I31" s="4" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>60</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/triple-hyaluronic-water-wave-sheet-mask</t>
+          <t>https://cosrx.com/products/peptide-132-hair-home-care-duo</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2218,12 +2212,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB003420</t>
+          <t>MB000754</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lip Plump Refresh AHA BHA Vitamin C: volumizador labial 20 g</t>
+          <t>Peptide-132 Ultra Perfect Hair Bonding Oil Serum: óleo-sérum para cabelo 28 ml · Single</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2234,21 +2228,27 @@
       <c r="D32" s="2" t="n">
         <v>137.9</v>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lip Plump - Refresh AHA BHA Vitamin C Lip Plumper</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>COSRX PEPTIDE-132 Ultra Perfect Hair Bonding Oil Serum</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
       <c r="H32" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="I32" s="4" t="n"/>
+      <c r="I32" s="4" t="n">
+        <v>23</v>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/lip-plump-refresh-aha-bha-viamin-c-lip-plumper</t>
+          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-oil-serum-번들?variant=52270495727832</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2271,12 +2271,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB003423</t>
+          <t>MB000753</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lip Sleep Balancium Ceramide Lip Butter: máscara labial noturna 20 g</t>
+          <t>Peptide-132 Ultra Perfect Hair Bonding Shampoo: shampoo reconstrutor para cabelo · 2-Pack / 200mL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2285,23 +2285,29 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>233.9</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lip Sleep - Balancium Ceramide Lip Butter Sleeping Mask</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>COSRX PEPTIDE-132 Ultra Perfect Hair Bonding Shampoo</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>200mL / 2-Pack</t>
+        </is>
+      </c>
       <c r="H33" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I33" s="4" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>46</v>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2309,7 +2315,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/lip-sleep-balancium-ceramide-lip-butter-sleeping-mask</t>
+          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-shampoo-번들?variant=52270322614488</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2324,12 +2330,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB003417</t>
+          <t>MB000752</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Low pH Good Night Soft Peeling Gel</t>
+          <t>Peptide-132 Ultra Perfect Hair Bonding Shampoo: shampoo reconstrutor para cabelo · Single / 100mL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2338,23 +2344,29 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>86.90000000000001</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Low pH Goodnight Soft Peeling Gel</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>COSRX PEPTIDE-132 Ultra Perfect Hair Bonding Shampoo</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>100mL / Single</t>
+        </is>
+      </c>
       <c r="H34" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I34" s="4" t="n"/>
+        <v>9.84</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2362,7 +2374,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/low-ph-goodnight-soft-peeling-gel-new</t>
+          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-shampoo-번들?variant=52270322680024</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2377,12 +2389,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB003390</t>
+          <t>MB000682</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Low pH Micellar Water with Niacinamide</t>
+          <t>Poreless Clarifying Charcoal Mask Pink: máscara de carvão para poros 110 g</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2391,29 +2403,23 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Low pH Niacinamide Micellar Cleansing Water</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Single (400mL)</t>
-        </is>
-      </c>
+          <t>Poreless Clarifying Charcoal Mask Pink</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>15</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I35" s="4" t="n"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2421,7 +2427,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/low-ph-niacinamide-micellar-cleansing-water?variant=43891424231640</t>
+          <t>https://cosrx.com/products/poreless-clarifying-charcoal-mask</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2436,12 +2442,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB000708</t>
+          <t>MB003375</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Low pH Niacinamide Micellar Cleansing Water: água micelar de pH baixo · 2-step Daily Deep Cleansing</t>
+          <t>Pure Fit Cica Calming True Sheet Mask: máscara calmante de centella (1 unidade)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2450,29 +2456,23 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>210.9</v>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>42.9</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Low pH Niacinamide Micellar Cleansing Water</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Single (400mL)</t>
-        </is>
-      </c>
+          <t>Pure Fit Cica Calming True Sheet Mask</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>15</v>
-      </c>
+        <v>6.99</v>
+      </c>
+      <c r="I36" s="4" t="n"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/low-ph-niacinamide-micellar-cleansing-water?variant=43891424231640</t>
+          <t>https://cosrx.com/products/pure-fit-cica-calming-true-sheet-mask</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2495,12 +2495,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB000709</t>
+          <t>MB003460</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Low pH Niacinamide Micellar Cleansing Water: água micelar de pH baixo · 3-step Total Cleansing Solution</t>
+          <t>Skin Barrier Moisturizing Body Cream: creme corporal com ceramidas 450 ml</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2509,29 +2509,23 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>327.9</v>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>181.9</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Low pH Niacinamide Micellar Cleansing Water</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Single (400mL)</t>
-        </is>
-      </c>
+          <t>COSRX Skin Barrier Moisturizing Body Cream</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>15</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I37" s="4" t="n"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2539,7 +2533,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/low-ph-niacinamide-micellar-cleansing-water?variant=43891424231640</t>
+          <t>https://cosrx.com/products/cosrx-skin-barrier-moisturizing-body-cream</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2554,12 +2548,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB003450</t>
+          <t>MB003412</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Master Patch Basic: adesivos para espinhas 12 mm (36 unidades)</t>
+          <t>The AHA BHA PHA LHA 35 Peel: peeling com 35% de ácidos 30 ml</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2568,25 +2562,21 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Master Patch Basic [36ea]</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>36ea</t>
-        </is>
-      </c>
+          <t>The AHA BHA PHA LHA 35 Peel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38" t="inlineStr">
@@ -2596,7 +2586,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/master-patch-basic-36-ea</t>
+          <t>https://cosrx.com/products/the-aha-bha-pha-lha-35-peel</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2611,12 +2601,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB003465</t>
+          <t>MB000640</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Master Patch Intensive: adesivos para espinhas em 2 tamanhos (90 unidades)</t>
+          <t>The Vitamin C 13 Serum: sérum com 13% de vitamina C pura 20 ml · Single</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2625,21 +2615,25 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>152.9</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Master Patch Intensive [90ea]</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>The Vitamin C 13 Serum</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
       <c r="H39" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I39" s="4" t="n"/>
       <c r="J39" t="inlineStr">
@@ -2649,7 +2643,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/master-patch-intensive-90ea_cpnp</t>
+          <t>https://cosrx.com/products/the-vitamin-c-13-serum-번들?variant=52270132789464</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2664,35 +2658,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB003448</t>
+          <t>MB003385</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>One Step Original Clear Pad: discos com BHA para poros e oleosidade (70 unidades)</t>
+          <t>Advanced Vitamin C 23 Serum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>152.9</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>One Step Original Clear Skin Calming Pad</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Advanced The Vitamin C 23 Serum</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
       <c r="H40" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I40" s="4" t="n"/>
       <c r="J40" t="inlineStr">
@@ -2702,7 +2700,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/one-step-original-clear-skin-calming-pad-new</t>
+          <t>https://cosrx.com/products/the-vitamin-c-23-serum?variant=52274189369560</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2717,38 +2715,38 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB003408</t>
+          <t>MB003407</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PDRN Glass Skin Duo: sérum 5 PDRN com colágeno + máscara peel-off Exosome</t>
+          <t>Daily Routine Kit with PDRN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>259.9</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>439.9</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PDRN Glass Skin Duo</t>
+          <t>PDRN Daily Routine Kit</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="4" t="n">
-        <v>35.7</v>
+        <v>60.35</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/pdrn-glass-skin-duo</t>
+          <t>https://cosrx.com/products/pdrn-daily-routine-kit_뉴번들</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2772,39 +2770,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB003406</t>
+          <t>MB003445</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PDRN Premium Routine Kit: tônico + sérum + máscaras + adesivos com PDRN</t>
+          <t>Galactomyces 95 Tone Balancing: essência</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>637.9</v>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>174.9</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PDRN Premium Routine Kit</t>
+          <t>Galactomyces 95 Tone Balancing Essence</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="4" t="n">
-        <v>89.25</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>105</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I42" s="4" t="n"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2812,7 +2808,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/pdrn-premium-routine-kit_뉴번들</t>
+          <t>https://cosrx.com/products/galactomyces-95-tone-balancing-essence</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2827,39 +2823,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB000688</t>
+          <t>MB003397</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Peptide Special Care Duo: adesivos para os olhos + máscaras de hidrogel com peptídeos</t>
+          <t>Hyaluronic Acid Serum 3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>234.9</v>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>126.9</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peptide Special Care Duo</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>The Hyaluronic Acid 3 Serum</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
       <c r="H43" s="4" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>38</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I43" s="4" t="n"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2867,7 +2865,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/peptide-special-care-duo</t>
+          <t>https://cosrx.com/products/the-hyaluronic-acid-3-serum_new-bundle?variant=52394633887960</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2882,12 +2880,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB000756</t>
+          <t>MB003452</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Peptide-132 Hair Bonding Mini Kit: shampoo + tratamento + óleo-sérum para cabelo</t>
+          <t>AC Collection Calming Liquid Intensive: essência calmante com própolis e BHA 125 ml</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2896,7 +2894,7 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>235.9</v>
+        <v>188.9</v>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
@@ -2905,16 +2903,18 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>COSRX PEPTIDE-132 Hair Bonding Mini Kit</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>AC Collection Calming Liquid Intensive</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>4.22 fl.oz / 125ml</t>
+        </is>
+      </c>
       <c r="H44" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>36</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I44" s="4" t="n"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-peptide-132-hair-bonding-mini-kit</t>
+          <t>https://cosrx.com/products/ac-collection-calming-liquid-intensive</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -2937,12 +2937,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB000686</t>
+          <t>MB003377</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Peptide-132 Hair Home Care Duo: shampoo 400 ml + máscara reconstrutora 240 ml</t>
+          <t>AC Collection: sérum para a aparência de manchas e marquinhas de espinhas</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>370.9</v>
+        <v>196.9</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -2960,16 +2960,18 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Peptide-132 Hair Home Care Duo</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>AC Collection Lightweight Soothing Moisturizer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2.70 fl.oz / 80ml</t>
+        </is>
+      </c>
       <c r="H45" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>60</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I45" s="4" t="n"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2977,7 +2979,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/peptide-132-hair-home-care-duo</t>
+          <t>https://cosrx.com/products/ac-collection-lightweight-soothing-moisturizer_cpnp</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -2992,12 +2994,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB000685</t>
+          <t>MB003434</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Peptide-132 Hair Home Care Kit: shampoo + tratamento + óleo-sérum em tamanho maior</t>
+          <t>Advanced Snail Peptide Eye Cream: creme para os olhos com caracol e peptídeos 25 ml</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3006,7 +3008,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>600.9</v>
+        <v>203.9</v>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
@@ -3015,16 +3017,18 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Peptide-132 Hair Home Care Kit</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Advanced Snail Peptide Eye Cream</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.85 fl.oz / 25ml</t>
+        </is>
+      </c>
       <c r="H46" s="4" t="n">
-        <v>82.45</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>97</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I46" s="4" t="n"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3032,7 +3036,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/peptide-132-hair-home-care-kit</t>
+          <t>https://cosrx.com/products/advanced-snail-peptide-eye-cream</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -3047,12 +3051,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB000754</t>
+          <t>MB003425</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Peptide-132 Ultra Perfect Hair Bonding Oil Serum: óleo-sérum para cabelo 28 ml · Single</t>
+          <t>Advanced Snail Radiance Dual Essence: essência dupla de caracol e niacinamida 80 ml</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3061,7 +3065,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>137.9</v>
+        <v>141.9</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -3070,20 +3074,18 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>COSRX PEPTIDE-132 Ultra Perfect Hair Bonding Oil Serum</t>
+          <t>Advanced Snail Radiance Dual Essence</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>2.70 fl.oz / 80ml</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>46</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I47" s="4" t="n"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3091,7 +3093,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-oil-serum-번들?variant=52270495760600</t>
+          <t>https://cosrx.com/products/advanced-snail-radiance-dual-essence</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3106,12 +3108,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB000753</t>
+          <t>MB000777</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Peptide-132 Ultra Perfect Hair Bonding Shampoo: shampoo reconstrutor para cabelo · 2-Pack / 200mL</t>
+          <t>COSRX Aloe Soothing Sun Cream FPS 50+ PA+++: protetor solar calmante de aloe 50 ml</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3120,7 +3122,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>233.9</v>
+        <v>115.9</v>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
@@ -3129,28 +3131,22 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>COSRX PEPTIDE-132 Ultra Perfect Hair Bonding Shampoo</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>200mL / 2-Pack</t>
-        </is>
-      </c>
+          <t>Aloe Soothing Sun Cream  SPF50+/ PA+++</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>46</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I48" s="4" t="n"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-shampoo-번들?variant=52270322614488</t>
+          <t>https://cosrx.com/products/aloe-soothing-sun-cream-spf50-pa</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3165,12 +3161,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB003447</t>
+          <t>MB003471</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pink Charcoal Clarifying Pore Mask</t>
+          <t>COSRX Red Rice &amp; Inositol Deep Pore Cleansing Exfoliator</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3179,7 +3175,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>138.9</v>
+        <v>144.9</v>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
@@ -3188,12 +3184,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Poreless Clarifying Charcoal Mask Pink</t>
+          <t>COSRX RED RICE INOSITOL Pore Clarifying Deep Cleanser</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I49" s="4" t="n"/>
       <c r="J49" t="inlineStr">
@@ -3203,7 +3199,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/poreless-clarifying-charcoal-mask</t>
+          <t>https://cosrx.com/products/cosrx-red-rice-inositol-pore-clarifying-deep-cleanser</t>
         </is>
       </c>
       <c r="L49" s="2">
@@ -3218,12 +3214,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB000682</t>
+          <t>MB003376</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Poreless Clarifying Charcoal Mask Pink: máscara de carvão para poros 110 g</t>
+          <t>Clear Fit Master Patch: adesivos ultrafinos e foscos para espinhas (18 unidades)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3232,7 +3228,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>137.9</v>
+        <v>42.9</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
@@ -3241,14 +3237,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Poreless Clarifying Charcoal Mask Pink</t>
+          <t>Clear Fit Master Patch</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I50" s="4" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>6.99</v>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3256,7 +3254,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/poreless-clarifying-charcoal-mask</t>
+          <t>https://cosrx.com/products/clear-fit-master-patch</t>
         </is>
       </c>
       <c r="L50" s="2">
@@ -3271,12 +3269,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB003375</t>
+          <t>MB000732</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pure Fit Cica Calming True Sheet Mask: máscara calmante de centella (1 unidade)</t>
+          <t>Full Fit Propolis Light Ampoule: ampola de própolis 30 ml</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3285,7 +3283,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>42.9</v>
+        <v>203.9</v>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
@@ -3294,12 +3292,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pure Fit Cica Calming True Sheet Mask</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Full fit Propolis Light Ampoule</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1.01 fl.oz/30ml</t>
+        </is>
+      </c>
       <c r="H51" s="4" t="n">
-        <v>6.99</v>
+        <v>28</v>
       </c>
       <c r="I51" s="4" t="n"/>
       <c r="J51" t="inlineStr">
@@ -3309,7 +3311,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/pure-fit-cica-calming-true-sheet-mask</t>
+          <t>https://cosrx.com/products/full-fit-propolis-light-ampoule_cpnp</t>
         </is>
       </c>
       <c r="L51" s="2">
@@ -3324,12 +3326,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB003436</t>
+          <t>MB003461</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pure Fit Cica Clear Cleansing Oil: óleo de limpeza leve com centella 200 ml</t>
+          <t>Full Fit Propolis Synergy Toner: tônico de própolis e mel</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3338,7 +3340,7 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>210.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
@@ -3347,16 +3349,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pure Fit Cica Clear Cleansing Oil</t>
+          <t>Full Fit Propolis Synergy Toner</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>6.67 fl.oz / 200mL</t>
+          <t>5.07 fl.oz / 150mL</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I52" s="4" t="n"/>
       <c r="J52" t="inlineStr">
@@ -3366,7 +3368,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/pure-fit-cica-clear-cleansing-oil</t>
+          <t>https://cosrx.com/products/full-fit-propolis-synergy-toner_cpnp</t>
         </is>
       </c>
       <c r="L52" s="2">
@@ -3381,12 +3383,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB003379</t>
+          <t>MB003382</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pure Fit Cica Cream: creme calmante de centella 50 ml</t>
+          <t>Hydrium Green Tea Aqua Soothing Gel Cream: gel-creme calmante de chá verde 50 ml</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3395,7 +3397,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>232.9</v>
+        <v>181.9</v>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
@@ -3404,7 +3406,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pure Fit Cica Cream</t>
+          <t>Hydrium Green Tea Aqua Soothing Gel Cream</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3413,17 +3415,17 @@
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I53" s="4" t="n"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/pure-fit-cica-cream</t>
+          <t>https://cosrx.com/products/hydrium-green-tea-aqua-soothing-gel-cream</t>
         </is>
       </c>
       <c r="L53" s="2">
@@ -3438,12 +3440,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB003374</t>
+          <t>MB003456</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pure Fit Cica Creamy Foam Cleanser: espuma de limpeza cremosa de centella 150 ml</t>
+          <t>Hydrium Moisture Power Enriched Cream: creme hidratante intensivo 50 ml</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3452,7 +3454,7 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>130.9</v>
+        <v>181.9</v>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
@@ -3461,16 +3463,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pure Fit Cica Creamy Foam Cleanser</t>
+          <t>Hydrium Moisture Power Enriched Cream</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5.07 fl.oz / 150ml</t>
+          <t>1.69 fl.oz / 50ml</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I54" s="4" t="n"/>
       <c r="J54" t="inlineStr">
@@ -3480,7 +3482,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/pure-fit-cica-creamy-foam-cleanser</t>
+          <t>https://cosrx.com/products/hydrium-moisture-power-enriched-cream</t>
         </is>
       </c>
       <c r="L54" s="2">
@@ -3495,12 +3497,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB000673</t>
+          <t>MB003417</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Refresh ABC Daily Toner: tônico com AHA, BHA e vitamina C · 9.46 fl.oz / 280mL</t>
+          <t>Low pH Good Night Soft Peeling Gel</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3509,7 +3511,7 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>203.9</v>
+        <v>116.9</v>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
@@ -3518,26 +3520,22 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Refresh ABC Daily Toner (AHA BHA Vitamin C)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>9.46 fl.oz / 280mL</t>
-        </is>
-      </c>
+          <t>Low pH Goodnight Soft Peeling Gel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I55" s="4" t="n"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/refresh-abc-daily-toner-aha-bha-vitamin-c?variant=37519737553052</t>
+          <t>https://cosrx.com/products/low-ph-goodnight-soft-peeling-gel-new</t>
         </is>
       </c>
       <c r="L55" s="2">
@@ -3552,12 +3550,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB003429</t>
+          <t>MB003448</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Revitalizing Sunscreen with Vitamin E SPF 50+</t>
+          <t>One Step Original Clear Pad: discos com BHA para poros e oleosidade (70 unidades)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3566,7 +3564,7 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>166.9</v>
+        <v>159.9</v>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
@@ -3575,12 +3573,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitamin E Vitalizing Sunscreen SPF 50+</t>
+          <t>One Step Original Clear Skin Calming Pad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I56" s="4" t="n"/>
       <c r="J56" t="inlineStr">
@@ -3590,7 +3588,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/vitamin-e-vitalizing-sunscreen-spf-50</t>
+          <t>https://cosrx.com/products/one-step-original-clear-skin-calming-pad-new</t>
         </is>
       </c>
       <c r="L56" s="2">
@@ -3605,12 +3603,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB003460</t>
+          <t>MB000685</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Skin Barrier Moisturizing Body Cream: creme corporal com ceramidas 450 ml</t>
+          <t>Peptide-132 Hair Home Care Kit: shampoo + tratamento + óleo-sérum em tamanho maior</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3619,7 +3617,7 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>181.9</v>
+        <v>600.9</v>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
@@ -3628,14 +3626,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>COSRX Skin Barrier Moisturizing Body Cream</t>
+          <t>Peptide-132 Hair Home Care Kit</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I57" s="4" t="n"/>
+        <v>82.45</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>97</v>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-skin-barrier-moisturizing-body-cream</t>
+          <t>https://cosrx.com/products/peptide-132-hair-home-care-kit</t>
         </is>
       </c>
       <c r="L57" s="2">
@@ -3658,12 +3658,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MB003412</t>
+          <t>MB003447</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The AHA BHA PHA LHA 35 Peel: peeling com 35% de ácidos 30 ml</t>
+          <t>Pink Charcoal Clarifying Pore Mask</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>137.9</v>
+        <v>138.9</v>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The AHA BHA PHA LHA 35 Peel</t>
+          <t>Poreless Clarifying Charcoal Mask Pink</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-aha-bha-pha-lha-35-peel</t>
+          <t>https://cosrx.com/products/poreless-clarifying-charcoal-mask</t>
         </is>
       </c>
       <c r="L58" s="2">
@@ -3711,12 +3711,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MB000648</t>
+          <t>MB003436</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Retinol 0.1 Cream: creme com 0,1% de retinol puro 20 ml · 2-Pack</t>
+          <t>Pure Fit Cica Clear Cleansing Oil: óleo de limpeza leve com centella 200 ml</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>353.9</v>
+        <v>210.9</v>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
@@ -3734,16 +3734,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>The Retinol 0.1 Cream</t>
+          <t>Pure Fit Cica Clear Cleansing Oil</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>6.67 fl.oz / 200mL</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="I59" s="4" t="n"/>
       <c r="J59" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-retinol-0-1-cream_new-bundle?variant=52394749886680</t>
+          <t>https://cosrx.com/products/pure-fit-cica-clear-cleansing-oil</t>
         </is>
       </c>
       <c r="L59" s="2">
@@ -3768,12 +3768,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MB000640</t>
+          <t>MB003379</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Vitamin C 13 Serum: sérum com 13% de vitamina C pura 20 ml · Single</t>
+          <t>Pure Fit Cica Cream: creme calmante de centella 50 ml</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>152.9</v>
+        <v>232.9</v>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
@@ -3791,28 +3791,26 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>The Vitamin C 13 Serum</t>
+          <t>Pure Fit Cica Cream</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>1.69 fl.oz / 50ml</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>42</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="I60" s="4" t="n"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-vitamin-c-13-serum-번들?variant=52270132822232</t>
+          <t>https://cosrx.com/products/pure-fit-cica-cream</t>
         </is>
       </c>
       <c r="L60" s="2">
@@ -3827,21 +3825,21 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB003438</t>
+          <t>MB003374</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AC Collection Lightweight Soothing Moisturizer</t>
+          <t>Pure Fit Cica Creamy Foam Cleanser: espuma de limpeza cremosa de centella 150 ml</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>138.9</v>
+        <v>130.9</v>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
@@ -3850,16 +3848,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AC Collection Lightweight Soothing Moisturizer</t>
+          <t>Pure Fit Cica Creamy Foam Cleanser</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2.70 fl.oz / 80ml</t>
+          <t>5.07 fl.oz / 150ml</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I61" s="4" t="n"/>
       <c r="J61" t="inlineStr">
@@ -3869,7 +3867,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/ac-collection-lightweight-soothing-moisturizer_cpnp</t>
+          <t>https://cosrx.com/products/pure-fit-cica-creamy-foam-cleanser</t>
         </is>
       </c>
       <c r="L61" s="2">
@@ -3884,21 +3882,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB003474</t>
+          <t>MB000673</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Advanced Snail Mucin Gel Cleanser</t>
+          <t>Refresh ABC Daily Toner: tônico com AHA, BHA e vitamina C · 9.46 fl.oz / 280mL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>42.9</v>
+        <v>203.9</v>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
@@ -3907,26 +3905,26 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Advanced Snail Mucin Gel Cleanser</t>
+          <t>Refresh ABC Daily Toner (AHA BHA Vitamin C)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>5.07 fl.oz / 150ml</t>
+          <t>9.46 fl.oz / 280mL</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I62" s="4" t="n"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/advanced-snail-mucin-gel-cleanser?variant=39848886108316</t>
+          <t>https://cosrx.com/products/refresh-abc-daily-toner-aha-bha-vitamin-c?variant=37519737553052</t>
         </is>
       </c>
       <c r="L62" s="2">
@@ -3941,21 +3939,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB003385</t>
+          <t>MB003429</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Advanced Vitamin C 23 Serum</t>
+          <t>Revitalizing Sunscreen with Vitamin E SPF 50+</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>152.9</v>
+        <v>166.9</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -3964,20 +3962,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Advanced The Vitamin C 23 Serum</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2-Pack</t>
-        </is>
-      </c>
+          <t>Vitamin E Vitalizing Sunscreen SPF 50+</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I63" s="4" t="n"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3985,7 +3977,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-vitamin-c-23-serum?variant=52274189402328</t>
+          <t>https://cosrx.com/products/vitamin-e-vitalizing-sunscreen-spf-50</t>
         </is>
       </c>
       <c r="L63" s="2">
@@ -4000,21 +3992,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB003407</t>
+          <t>MB000648</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Daily Routine Kit with PDRN</t>
+          <t>The Retinol 0.1 Cream: creme com 0,1% de retinol puro 20 ml · 2-Pack</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>439.9</v>
+        <v>353.9</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -4023,16 +4015,18 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PDRN Daily Routine Kit</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>The Retinol 0.1 Cream</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2-Pack</t>
+        </is>
+      </c>
       <c r="H64" s="4" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="I64" s="4" t="n">
-        <v>71</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="I64" s="4" t="n"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4040,7 +4034,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/pdrn-daily-routine-kit_뉴번들</t>
+          <t>https://cosrx.com/products/the-retinol-0-1-cream_new-bundle?variant=52394749886680</t>
         </is>
       </c>
       <c r="L64" s="2">
@@ -4055,12 +4049,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB003445</t>
+          <t>MB003438</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Galactomyces 95 Tone Balancing: essência</t>
+          <t>AC Collection Lightweight Soothing Moisturizer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4069,7 +4063,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>174.9</v>
+        <v>138.9</v>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
@@ -4078,12 +4072,16 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Galactomyces 95 Tone Balancing Essence</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>AC Collection Lightweight Soothing Moisturizer</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2.70 fl.oz / 80ml</t>
+        </is>
+      </c>
       <c r="H65" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I65" s="4" t="n"/>
       <c r="J65" t="inlineStr">
@@ -4093,7 +4091,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/galactomyces-95-tone-balancing-essence</t>
+          <t>https://cosrx.com/products/ac-collection-lightweight-soothing-moisturizer_cpnp</t>
         </is>
       </c>
       <c r="L65" s="2">
@@ -4108,12 +4106,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB003397</t>
+          <t>MB003474</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hyaluronic Acid Serum 3</t>
+          <t>Advanced Snail Mucin Gel Cleanser</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4122,7 +4120,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>126.9</v>
+        <v>42.9</v>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
@@ -4131,16 +4129,16 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>The Hyaluronic Acid 3 Serum</t>
+          <t>Advanced Snail Mucin Gel Cleanser</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>5.07 fl.oz / 150ml</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I66" s="4" t="n"/>
       <c r="J66" t="inlineStr">
@@ -4150,7 +4148,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-hyaluronic-acid-3-serum_new-bundle?variant=52394633920728</t>
+          <t>https://cosrx.com/products/advanced-snail-mucin-gel-cleanser?variant=39848886108316</t>
         </is>
       </c>
       <c r="L66" s="2">
@@ -4303,11 +4301,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I69" s="4" t="n"/>
       <c r="J69" t="inlineStr">
@@ -4317,7 +4315,7 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-retinol-0-1-cream_new-bundle?variant=52394749886680</t>
+          <t>https://cosrx.com/products/the-retinol-0-1-cream_new-bundle?variant=52394749853912</t>
         </is>
       </c>
       <c r="L69" s="2">
@@ -4360,11 +4358,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I70" s="4" t="n"/>
       <c r="J70" t="inlineStr">
@@ -4374,7 +4372,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-retinol-0-1-cream_new-bundle?variant=52394749886680</t>
+          <t>https://cosrx.com/products/the-retinol-0-1-cream_new-bundle?variant=52394749853912</t>
         </is>
       </c>
       <c r="L70" s="2">
@@ -4641,14 +4639,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>240mL / 2-Pack</t>
+          <t>240mL / Single</t>
         </is>
       </c>
       <c r="H75" s="4" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4657,7 +4655,7 @@
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-treatment-번들?variant=52270432190680</t>
+          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-treatment-번들?variant=52270432157912</t>
         </is>
       </c>
       <c r="L75" s="2">
@@ -4700,14 +4698,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4716,7 +4714,7 @@
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-oil-serum-번들?variant=52270495760600</t>
+          <t>https://cosrx.com/products/cosrx-peptide-132-ultra-perfect-hair-bonding-oil-serum-번들?variant=52270495727832</t>
         </is>
       </c>
       <c r="L76" s="2">
@@ -5203,15 +5201,13 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I85" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I85" s="4" t="n"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5219,7 +5215,7 @@
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-6-peptide-skin-booster-serum-bundle?variant=52315200291032</t>
+          <t>https://cosrx.com/products/the-6-peptide-skin-booster-serum-bundle?variant=52315200258264</t>
         </is>
       </c>
       <c r="L85" s="2">
@@ -5315,15 +5311,13 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I87" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I87" s="4" t="n"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5331,7 +5325,7 @@
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-alpha-arbutin-2-discoloration-care-serum?variant=52270298431704</t>
+          <t>https://cosrx.com/products/the-alpha-arbutin-2-discoloration-care-serum?variant=52270298398936</t>
         </is>
       </c>
       <c r="L87" s="2">
@@ -5369,12 +5363,16 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Full Fit Propolis Honey Overnight Mask</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>Full fit Propolis Light Ampoule</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1.01 fl.oz/30ml</t>
+        </is>
+      </c>
       <c r="H88" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I88" s="4" t="n"/>
       <c r="J88" t="inlineStr">
@@ -5384,7 +5382,7 @@
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/full-fit-propolis-honey-overnight-mask_cpnp</t>
+          <t>https://cosrx.com/products/full-fit-propolis-light-ampoule_cpnp</t>
         </is>
       </c>
       <c r="L88" s="2">
@@ -5427,15 +5425,13 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I89" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I89" s="4" t="n"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5443,7 +5439,7 @@
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-6-peptide-skin-booster-serum-bundle?variant=52315200291032</t>
+          <t>https://cosrx.com/products/the-6-peptide-skin-booster-serum-bundle?variant=52315200258264</t>
         </is>
       </c>
       <c r="L89" s="2">
@@ -5534,12 +5530,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Full Fit Propolis Honey Overnight Mask</t>
+          <t>Full Fit Propolis Light Cream - Jar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" s="4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I91" s="4" t="n"/>
       <c r="J91" t="inlineStr">
@@ -5549,7 +5545,7 @@
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/full-fit-propolis-honey-overnight-mask_cpnp</t>
+          <t>https://cosrx.com/products/full-fit-propolis-light-cream-jar-global</t>
         </is>
       </c>
       <c r="L91" s="2">
@@ -5592,15 +5588,13 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I92" s="4" t="n">
-        <v>50</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I92" s="4" t="n"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5608,7 +5602,7 @@
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-niacinamide-15-serum-번들?variant=52274229543128</t>
+          <t>https://cosrx.com/products/the-niacinamide-15-serum-번들?variant=52274229510360</t>
         </is>
       </c>
       <c r="L92" s="2">
@@ -5651,15 +5645,13 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H93" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="I93" s="4" t="n">
-        <v>42</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I93" s="4" t="n"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5667,7 +5659,7 @@
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-vitamin-c-13-serum-번들?variant=52270132822232</t>
+          <t>https://cosrx.com/products/the-vitamin-c-13-serum-번들?variant=52270132789464</t>
         </is>
       </c>
       <c r="L93" s="2">
@@ -5758,16 +5750,16 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>The Retinol 0.1 Cream</t>
+          <t>The Retinol 0.5 Oil</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="H95" s="4" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I95" s="4" t="n"/>
       <c r="J95" t="inlineStr">
@@ -5777,7 +5769,7 @@
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>https://cosrx.com/products/the-retinol-0-1-cream_new-bundle?variant=52394749886680</t>
+          <t>https://cosrx.com/products/the-retinol-0-5-oil-번들?variant=52274235572440</t>
         </is>
       </c>
       <c r="L95" s="2">
@@ -8660,7 +8652,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
@@ -8690,7 +8686,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
@@ -9091,7 +9091,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
@@ -9121,7 +9125,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
@@ -9151,7 +9159,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
@@ -9181,7 +9193,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
@@ -9558,7 +9574,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
@@ -9588,7 +9608,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
@@ -9678,7 +9702,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
@@ -9708,7 +9736,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
@@ -9768,7 +9800,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
@@ -9798,7 +9834,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
@@ -9858,7 +9898,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
@@ -9888,7 +9932,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
@@ -9948,7 +9996,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
@@ -9978,7 +10030,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
@@ -13593,7 +13649,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
@@ -13623,7 +13683,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
@@ -13734,7 +13798,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
@@ -13764,7 +13832,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
@@ -13942,7 +14014,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
@@ -13972,7 +14048,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
@@ -14053,7 +14133,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
@@ -14080,7 +14164,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
@@ -14137,7 +14225,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
@@ -14167,7 +14259,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
@@ -14251,7 +14347,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
@@ -14281,7 +14381,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
@@ -14335,7 +14439,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
@@ -14362,7 +14470,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
@@ -14419,7 +14531,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
@@ -14449,7 +14565,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
@@ -14506,7 +14626,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
@@ -14536,7 +14660,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr">
         <is>
@@ -14593,7 +14721,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
@@ -14623,7 +14755,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
         <is>
@@ -14791,7 +14927,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
@@ -14821,7 +14961,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
@@ -15219,7 +15363,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://cosrx.com · loja "COSRX Official" · moeda USD · lido em 30/10/2026 06:02 UTC</t>
+          <t>Site oficial: https://cosrx.com · loja "COSRX Official" · moeda USD · lido em 30/10/2026 06:03 UTC</t>
         </is>
       </c>
     </row>
